--- a/SGC-CKN/Excel/62c17e24-d417-48cb-8a4e-9a1690b56e78_Xã_Thường_Tín__Tam_Hưng__Thượng_Phúc__Dân_Hòa__TP_Hà_Nội_C1-539_D1200_09-04-2026.xlsx
+++ b/SGC-CKN/Excel/62c17e24-d417-48cb-8a4e-9a1690b56e78_Xã_Thường_Tín__Tam_Hưng__Thượng_Phúc__Dân_Hòa__TP_Hà_Nội_C1-539_D1200_09-04-2026.xlsx
@@ -53,7 +53,7 @@
     <t>Bắt đầu thi công</t>
   </si>
   <si>
-    <t>16:15 08/04/2026</t>
+    <t>08:20 09/04/2026</t>
   </si>
   <si>
     <t>Kết thúc thi công</t>
